--- a/resources/formatos/FormatoCotaTerreno.xlsx
+++ b/resources/formatos/FormatoCotaTerreno.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\E-monitoring-V5\resources\formatos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\E-Monitoring-SqlServer\resources\formatos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C79B65C-7B08-4634-9CF1-3A792216E41F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B4AB15-3C8B-46C5-AF12-63F39283458B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cota Terreno" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>Fecha</t>
   </si>
@@ -49,18 +54,23 @@
     <t>Terreno1</t>
   </si>
   <si>
-    <t>Los datos no debe contener fórmulas y el Formato de fecha: día/mes/año completo</t>
+    <t>* Los datos no debe contener fórmulas y el Formato de fecha: día/mes/año completo.</t>
+  </si>
+  <si>
+    <t>* El formato de hora: hh:mm:ss</t>
+  </si>
+  <si>
+    <t>DATOS DEL TERRENO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
-    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -88,12 +98,21 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -106,8 +125,14 @@
         <bgColor rgb="FF00796B"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="21">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -119,35 +144,206 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
+      <right/>
+      <top style="thin">
         <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
         <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      </left>
       <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -155,187 +351,117 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -343,73 +469,110 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -437,7 +600,7 @@
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5238750" cy="1428750"/>
+    <xdr:ext cx="1260000" cy="1260000"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
@@ -456,6 +619,10 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1260000" cy="1260000"/>
+        </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -751,145 +918,143 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7"/>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-    </row>
-    <row r="2" spans="1:4" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-    </row>
-    <row r="3" spans="1:4" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-    </row>
-    <row r="4" spans="1:4" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-    </row>
-    <row r="5" spans="1:4" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-    </row>
-    <row r="6" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+    <row r="1" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="20"/>
+      <c r="B1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="10"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="13"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="13"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="14"/>
-      <c r="B9" s="15"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="27"/>
+    </row>
+    <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="21"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="29"/>
+    </row>
+    <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="21"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="29"/>
+    </row>
+    <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="22"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="32"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="24"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="35"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="17"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="19"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="12"/>
+      <c r="B9" s="13"/>
       <c r="C9" s="15"/>
       <c r="D9" s="16"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="21"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="22"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="24"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="6" t="s">
+      <c r="B10" s="9"/>
+      <c r="C10" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="6"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+      <c r="D10" s="7"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="B11" s="6"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
         <v>44166</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C15">
+      <c r="C13">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>43861</v>
-      </c>
-      <c r="B16" s="3" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="3">
+        <v>44180</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C16">
+      <c r="C14">
         <v>0</v>
       </c>
     </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C20" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A1:D5"/>
-    <mergeCell ref="A6:D9"/>
-    <mergeCell ref="A10:D11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:D12"/>
+  <mergeCells count="10">
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="B1:D4"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
